--- a/rmonize/data_proc_elem/DPE_NAKO_P1.xlsx
+++ b/rmonize/data_proc_elem/DPE_NAKO_P1.xlsx
@@ -437,7 +437,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>ID</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">

--- a/rmonize/data_proc_elem/DPE_NAKO_P1.xlsx
+++ b/rmonize/data_proc_elem/DPE_NAKO_P1.xlsx
@@ -792,7 +792,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>gcal</t>
+          <t>a_nu_gcal</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
